--- a/sources/excels/CPE_Courses.xlsx
+++ b/sources/excels/CPE_Courses.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ajdan\OneDrive\Documents\GitHub\fixedOOP2\Final-OOP2\sources\excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FD916D9-58F5-4F38-AB46-436DAFA7D699}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B453E0D-FC49-445B-BE8B-9F846C3147A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{1AA50959-B7E8-463A-BB77-82FF90CA8362}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{1AA50959-B7E8-463A-BB77-82FF90CA8362}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1474,6 +1474,12 @@
       <c r="P16" s="3"/>
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>8</v>
+      </c>
       <c r="K17" s="1" t="s">
         <v>86</v>
       </c>
@@ -1485,10 +1491,10 @@
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E18" s="5" t="s">
         <v>180</v>
@@ -1504,10 +1510,10 @@
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>146</v>
@@ -1517,10 +1523,10 @@
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>147</v>
@@ -1541,10 +1547,10 @@
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>149</v>
@@ -1560,10 +1566,10 @@
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>148</v>
@@ -1577,10 +1583,10 @@
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E23" s="3" t="s">
         <v>150</v>
@@ -1594,10 +1600,10 @@
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>151</v>
@@ -1605,10 +1611,10 @@
     </row>
     <row r="25" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="K25" s="1" t="s">
         <v>19</v>
@@ -1619,10 +1625,10 @@
     </row>
     <row r="26" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E26" s="5" t="s">
         <v>181</v>
@@ -1636,10 +1642,10 @@
     </row>
     <row r="27" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E27" s="3" t="s">
         <v>152</v>
@@ -1650,10 +1656,10 @@
     </row>
     <row r="28" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E28" s="3" t="s">
         <v>153</v>
@@ -1669,10 +1675,10 @@
     </row>
     <row r="29" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="E29" s="3" t="s">
         <v>154</v>
@@ -1683,10 +1689,10 @@
     </row>
     <row r="30" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="E30" s="3" t="s">
         <v>155</v>
@@ -1697,10 +1703,10 @@
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E31" s="3" t="s">
         <v>156</v>
@@ -1711,10 +1717,10 @@
     </row>
     <row r="32" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E32" s="3" t="s">
         <v>157</v>
@@ -1724,18 +1730,18 @@
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="E34" s="5" t="s">
         <v>184</v>
@@ -1744,10 +1750,10 @@
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E35" s="3" t="s">
         <v>164</v>
@@ -1755,10 +1761,10 @@
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E36" s="3" t="s">
         <v>165</v>
@@ -1771,10 +1777,10 @@
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="E37" s="3" t="s">
         <v>166</v>
@@ -1783,10 +1789,10 @@
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>98</v>
+        <v>108</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="E38" s="3" t="s">
         <v>167</v>
@@ -1795,10 +1801,10 @@
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E39" s="3" t="s">
         <v>168</v>
@@ -1807,19 +1813,19 @@
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="L40" s="3"/>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="E41" s="5" t="s">
         <v>183</v>
@@ -1828,10 +1834,10 @@
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E42" s="3" t="s">
         <v>169</v>
@@ -1839,10 +1845,10 @@
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E43" s="3" t="s">
         <v>170</v>
@@ -1854,10 +1860,10 @@
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D44" s="3"/>
       <c r="E44" s="3" t="s">
@@ -1870,10 +1876,10 @@
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="D45" s="3"/>
       <c r="E45" s="3" t="s">
@@ -1884,19 +1890,19 @@
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="L46" s="3"/>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="E47" s="5" t="s">
         <v>182</v>
@@ -1905,10 +1911,10 @@
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="E48" s="3" t="s">
         <v>158</v>
@@ -1917,10 +1923,10 @@
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E49" s="3" t="s">
         <v>159</v>
@@ -1934,10 +1940,10 @@
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
-        <v>138</v>
+        <v>68</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>139</v>
+        <v>69</v>
       </c>
       <c r="E50" s="3" t="s">
         <v>160</v>
@@ -1946,10 +1952,10 @@
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
-        <v>68</v>
+        <v>86</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>69</v>
+        <v>87</v>
       </c>
       <c r="E51" s="3" t="s">
         <v>161</v>
@@ -1957,22 +1963,16 @@
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
-        <v>86</v>
+        <v>100</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>87</v>
+        <v>101</v>
       </c>
       <c r="E52" s="3" t="s">
         <v>162</v>
       </c>
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A53" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="B53" s="1" t="s">
-        <v>101</v>
-      </c>
       <c r="E53" s="3" t="s">
         <v>163</v>
       </c>
